--- a/URBN.xlsx
+++ b/URBN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1874CA08-9EFA-45E9-966C-8CED67D2E3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0496A15-73AA-4132-A7CC-B82FF9E79C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{74F0CBED-AE29-49BC-826C-5A327DCF0A9C}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{74F0CBED-AE29-49BC-826C-5A327DCF0A9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -232,13 +232,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -301,38 +307,38 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -692,7 +698,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="2">
-        <v>74.28</v>
+        <v>79.900000000000006</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -700,10 +706,10 @@
         <v>5</v>
       </c>
       <c r="J3" s="3">
-        <v>87.503853000000007</v>
+        <v>85.633606999999998</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -715,7 +721,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>6499.7862008400007</v>
+        <v>6842.1251993000005</v>
       </c>
       <c r="K4" s="4"/>
     </row>
@@ -727,11 +733,11 @@
         <v>7</v>
       </c>
       <c r="J5" s="3">
-        <f>301.364+111.978</f>
-        <v>413.34199999999998</v>
+        <f>598.756+117.371</f>
+        <v>716.12699999999995</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -742,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -751,7 +757,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>6086.444200840001</v>
+        <v>6125.9981993000001</v>
       </c>
     </row>
   </sheetData>
@@ -814,16 +820,16 @@
       <c r="N2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="Q2" s="18" t="s">
+      <c r="Q2" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="R2" s="16" t="s">
         <v>60</v>
       </c>
     </row>
@@ -862,7 +868,9 @@
       <c r="O3" s="6">
         <v>252</v>
       </c>
-      <c r="P3" s="6"/>
+      <c r="P3" s="6">
+        <v>252</v>
+      </c>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
     </row>
@@ -901,7 +909,9 @@
       <c r="O4" s="6">
         <v>256</v>
       </c>
-      <c r="P4" s="6"/>
+      <c r="P4" s="6">
+        <v>257</v>
+      </c>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
     </row>
@@ -942,7 +952,9 @@
       <c r="O5" s="6">
         <v>276</v>
       </c>
-      <c r="P5" s="6"/>
+      <c r="P5" s="6">
+        <v>284</v>
+      </c>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
     </row>
@@ -981,7 +993,9 @@
       <c r="O6" s="6">
         <v>8</v>
       </c>
-      <c r="P6" s="6"/>
+      <c r="P6" s="6">
+        <v>8</v>
+      </c>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
     </row>
@@ -1019,7 +1033,7 @@
         <v>731</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" ref="J7:O7" si="1">+SUM(J3:J6)</f>
+        <f t="shared" ref="J7:P7" si="1">+SUM(J3:J6)</f>
         <v>733</v>
       </c>
       <c r="K7" s="8">
@@ -1042,7 +1056,10 @@
         <f t="shared" si="1"/>
         <v>792</v>
       </c>
-      <c r="P7" s="9"/>
+      <c r="P7" s="8">
+        <f t="shared" si="1"/>
+        <v>801</v>
+      </c>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
     </row>
@@ -1081,7 +1098,9 @@
       <c r="O8" s="6">
         <v>9</v>
       </c>
-      <c r="P8" s="7"/>
+      <c r="P8" s="17">
+        <v>9</v>
+      </c>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
     </row>
@@ -1107,8 +1126,12 @@
       <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+      <c r="C10" s="10">
+        <v>473.64</v>
+      </c>
+      <c r="D10" s="10">
+        <v>530.08699999999999</v>
+      </c>
       <c r="E10" s="10">
         <v>549.81899999999996</v>
       </c>
@@ -1142,7 +1165,9 @@
       <c r="O10" s="7">
         <v>589.07299999999998</v>
       </c>
-      <c r="P10" s="7"/>
+      <c r="P10" s="7">
+        <v>634.53499999999997</v>
+      </c>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
     </row>
@@ -1150,8 +1175,12 @@
       <c r="B11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="C11" s="10">
+        <v>273.73500000000001</v>
+      </c>
+      <c r="D11" s="10">
+        <v>331.20100000000002</v>
+      </c>
       <c r="E11" s="10">
         <v>331.77199999999999</v>
       </c>
@@ -1185,7 +1214,9 @@
       <c r="O11" s="7">
         <v>411.71899999999999</v>
       </c>
-      <c r="P11" s="7"/>
+      <c r="P11" s="7">
+        <v>478.053</v>
+      </c>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
     </row>
@@ -1193,8 +1224,12 @@
       <c r="B12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="10">
+        <v>308.70800000000003</v>
+      </c>
+      <c r="D12" s="10">
+        <v>346.42399999999998</v>
+      </c>
       <c r="E12" s="10">
         <v>324.375</v>
       </c>
@@ -1228,7 +1263,9 @@
       <c r="O12" s="7">
         <v>304.72699999999998</v>
       </c>
-      <c r="P12" s="7"/>
+      <c r="P12" s="7">
+        <v>360.01499999999999</v>
+      </c>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
     </row>
@@ -1236,8 +1273,12 @@
       <c r="B13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="C13" s="10">
+        <v>51.47</v>
+      </c>
+      <c r="D13" s="10">
+        <v>55.792999999999999</v>
+      </c>
       <c r="E13" s="10">
         <v>65.516000000000005</v>
       </c>
@@ -1271,7 +1312,9 @@
       <c r="O13" s="7">
         <v>167.26400000000001</v>
       </c>
-      <c r="P13" s="7"/>
+      <c r="P13" s="7">
+        <v>178.60499999999999</v>
+      </c>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
     </row>
@@ -1279,8 +1322,12 @@
       <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="C14" s="10">
+        <v>6.1210000000000004</v>
+      </c>
+      <c r="D14" s="10">
+        <v>8.69</v>
+      </c>
       <c r="E14" s="10">
         <v>9.6920000000000002</v>
       </c>
@@ -1314,7 +1361,9 @@
       <c r="O14" s="7">
         <v>8.5619999999999994</v>
       </c>
-      <c r="P14" s="7"/>
+      <c r="P14" s="7">
+        <v>10.707000000000001</v>
+      </c>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
     </row>
@@ -1322,8 +1371,12 @@
       <c r="B15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="C15" s="10">
+        <v>1004.101</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1160.0889999999999</v>
+      </c>
       <c r="E15" s="10">
         <v>1145.7660000000001</v>
       </c>
@@ -1357,7 +1410,9 @@
       <c r="O15" s="7">
         <v>1220.914</v>
       </c>
-      <c r="P15" s="7"/>
+      <c r="P15" s="7">
+        <v>1392.52</v>
+      </c>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
     </row>
@@ -1365,8 +1420,12 @@
       <c r="B16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="C16" s="10">
+        <v>51.47</v>
+      </c>
+      <c r="D16" s="10">
+        <v>55.792999999999999</v>
+      </c>
       <c r="E16" s="10">
         <v>65.516000000000005</v>
       </c>
@@ -1400,7 +1459,9 @@
       <c r="O16" s="7">
         <v>167.26400000000001</v>
       </c>
-      <c r="P16" s="7"/>
+      <c r="P16" s="7">
+        <v>178.60499999999999</v>
+      </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
     </row>
@@ -1408,8 +1469,12 @@
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="C17" s="10">
+        <v>58.103000000000002</v>
+      </c>
+      <c r="D17" s="10">
+        <v>56.313000000000002</v>
+      </c>
       <c r="E17" s="10">
         <v>69.891999999999996</v>
       </c>
@@ -1443,7 +1508,9 @@
       <c r="O17" s="7">
         <v>93.167000000000002</v>
       </c>
-      <c r="P17" s="7"/>
+      <c r="P17" s="7">
+        <v>90.79</v>
+      </c>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
     </row>
@@ -1451,8 +1518,12 @@
       <c r="B18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
+      <c r="C18" s="9">
+        <v>1113.6574000000001</v>
+      </c>
+      <c r="D18" s="9">
+        <v>1272.1949999999999</v>
+      </c>
       <c r="E18" s="9">
         <v>1281.174</v>
       </c>
@@ -1486,7 +1557,9 @@
       <c r="O18" s="9">
         <v>1481.345</v>
       </c>
-      <c r="P18" s="7"/>
+      <c r="P18" s="9">
+        <v>1661.915</v>
+      </c>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
       <c r="S18" s="3"/>
@@ -1536,8 +1609,12 @@
       <c r="B19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
+      <c r="C19" s="11">
+        <v>742.44299999999998</v>
+      </c>
+      <c r="D19" s="7">
+        <v>816.61400000000003</v>
+      </c>
       <c r="E19" s="7">
         <f>825.375+1.392</f>
         <v>826.76700000000005</v>
@@ -1573,7 +1650,9 @@
       <c r="O19" s="7">
         <v>938.779</v>
       </c>
-      <c r="P19" s="7"/>
+      <c r="P19" s="7">
+        <v>940.36400000000003</v>
+      </c>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
       <c r="S19" s="3"/>
@@ -1625,11 +1704,11 @@
       </c>
       <c r="C20" s="3">
         <f t="shared" ref="C20:H20" si="2">+C18-C19</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="3">
+        <v>371.21440000000007</v>
+      </c>
+      <c r="D20" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>455.5809999999999</v>
       </c>
       <c r="E20" s="3">
         <f t="shared" si="2"/>
@@ -1652,7 +1731,7 @@
         <v>497.31900000000007</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" ref="J20:O20" si="3">+J18-J19</f>
+        <f t="shared" ref="J20:P20" si="3">+J18-J19</f>
         <v>527.68099999999981</v>
       </c>
       <c r="K20" s="3">
@@ -1675,7 +1754,10 @@
         <f t="shared" si="3"/>
         <v>542.56600000000003</v>
       </c>
-      <c r="P20" s="3"/>
+      <c r="P20" s="3">
+        <f t="shared" si="3"/>
+        <v>721.55099999999993</v>
+      </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
@@ -1725,8 +1807,12 @@
       <c r="B21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="C21" s="3">
+        <v>299.84800000000001</v>
+      </c>
+      <c r="D21" s="7">
+        <v>323.483</v>
+      </c>
       <c r="E21" s="3">
         <v>345.42899999999997</v>
       </c>
@@ -1759,7 +1845,9 @@
       <c r="O21" s="3">
         <v>402.88499999999999</v>
       </c>
-      <c r="P21" s="3"/>
+      <c r="P21" s="3">
+        <v>432.81200000000001</v>
+      </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
@@ -1811,11 +1899,11 @@
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:H22" si="4">+C20-C21</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="3">
+        <v>71.366400000000056</v>
+      </c>
+      <c r="D22" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>132.0979999999999</v>
       </c>
       <c r="E22" s="3">
         <f t="shared" si="4"/>
@@ -1838,7 +1926,7 @@
         <v>128.69100000000009</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" ref="J22:O22" si="5">+J20-J21</f>
+        <f t="shared" ref="J22:P22" si="5">+J20-J21</f>
         <v>125.31399999999979</v>
       </c>
       <c r="K22" s="3">
@@ -1861,7 +1949,10 @@
         <f t="shared" si="5"/>
         <v>139.68100000000004</v>
       </c>
-      <c r="P22" s="3"/>
+      <c r="P22" s="3">
+        <f t="shared" si="5"/>
+        <v>288.73899999999992</v>
+      </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
@@ -1911,8 +2002,12 @@
       <c r="B23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="C23" s="3">
+        <v>1.0189999999999999</v>
+      </c>
+      <c r="D23" s="7">
+        <v>3.399</v>
+      </c>
       <c r="E23" s="3">
         <v>0.70499999999999996</v>
       </c>
@@ -1944,7 +2039,9 @@
       <c r="O23" s="3">
         <v>6.1849999999999996</v>
       </c>
-      <c r="P23" s="3"/>
+      <c r="P23" s="3">
+        <v>9.8010000000000002</v>
+      </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
@@ -1996,11 +2093,11 @@
       </c>
       <c r="C24" s="3">
         <f t="shared" ref="C24:H24" si="6">+C22+C23</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="3">
+        <v>72.385400000000061</v>
+      </c>
+      <c r="D24" s="7">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>135.4969999999999</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="6"/>
@@ -2023,7 +2120,7 @@
         <v>135.83200000000008</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" ref="J24:O24" si="7">+J22+J23</f>
+        <f t="shared" ref="J24:P24" si="7">+J22+J23</f>
         <v>130.90599999999981</v>
       </c>
       <c r="K24" s="3">
@@ -2046,7 +2143,10 @@
         <f t="shared" si="7"/>
         <v>145.86600000000004</v>
       </c>
-      <c r="P24" s="3"/>
+      <c r="P24" s="3">
+        <f t="shared" si="7"/>
+        <v>298.53999999999991</v>
+      </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
@@ -2096,8 +2196,12 @@
       <c r="B25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="C25" s="3">
+        <v>19.585000000000001</v>
+      </c>
+      <c r="D25" s="7">
+        <v>31.405000000000001</v>
+      </c>
       <c r="E25" s="3">
         <v>26.669</v>
       </c>
@@ -2129,7 +2233,9 @@
       <c r="O25" s="3">
         <v>30.161000000000001</v>
       </c>
-      <c r="P25" s="3"/>
+      <c r="P25" s="3">
+        <v>57.889000000000003</v>
+      </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
@@ -2181,11 +2287,11 @@
       </c>
       <c r="C26" s="3">
         <f t="shared" ref="C26:H26" si="8">+C24-C25</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="3">
+        <v>52.80040000000006</v>
+      </c>
+      <c r="D26" s="7">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>104.0919999999999</v>
       </c>
       <c r="E26" s="3">
         <f t="shared" si="8"/>
@@ -2208,7 +2314,7 @@
         <v>102.91100000000009</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" ref="J26:O26" si="9">+J24-J25</f>
+        <f t="shared" ref="J26:P26" si="9">+J24-J25</f>
         <v>120.3009999999998</v>
       </c>
       <c r="K26" s="3">
@@ -2231,7 +2337,10 @@
         <f t="shared" si="9"/>
         <v>115.70500000000004</v>
       </c>
-      <c r="P26" s="3"/>
+      <c r="P26" s="3">
+        <f t="shared" si="9"/>
+        <v>240.6509999999999</v>
+      </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
@@ -2341,59 +2450,62 @@
       <c r="B28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="14" t="e">
+      <c r="C28" s="12">
         <f t="shared" ref="C28:H28" si="10">+C26/C29</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D28" s="14" t="e">
+        <v>0.57097137759469985</v>
+      </c>
+      <c r="D28" s="12">
+        <f t="shared" si="10"/>
+        <v>1.1223838790083711</v>
+      </c>
+      <c r="E28" s="12">
+        <f t="shared" si="10"/>
+        <v>0.89473314805349191</v>
+      </c>
+      <c r="F28" s="12">
+        <f t="shared" si="10"/>
+        <v>0.51463372102672778</v>
+      </c>
+      <c r="G28" s="12">
+        <f t="shared" si="10"/>
+        <v>0.66325139892192531</v>
+      </c>
+      <c r="H28" s="12" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E28" s="14">
-        <f t="shared" si="10"/>
-        <v>0.89473314805349191</v>
-      </c>
-      <c r="F28" s="14">
-        <f t="shared" si="10"/>
-        <v>0.51463372102672778</v>
-      </c>
-      <c r="G28" s="14">
-        <f t="shared" si="10"/>
-        <v>0.66325139892192531</v>
-      </c>
-      <c r="H28" s="14" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I28" s="14">
+      <c r="I28" s="12">
         <f>+I26/I29</f>
         <v>1.1153175438373473</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="12">
         <f t="shared" ref="J28:K28" si="11">+J26/J29</f>
         <v>1.3036594728452351</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="12">
         <f t="shared" si="11"/>
         <v>1.1807537519887217</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L28" s="12">
         <f>+L26/L29</f>
         <v>1.6044283449074521</v>
       </c>
-      <c r="M28" s="14">
+      <c r="M28" s="12">
         <f>+M26/M29</f>
         <v>1.2980157763076512</v>
       </c>
-      <c r="N28" s="14">
+      <c r="N28" s="12">
         <f>+N26/N29</f>
         <v>1.0733148390082932</v>
       </c>
-      <c r="O28" s="14">
+      <c r="O28" s="12">
         <f>+O26/O29</f>
         <v>1.3222846312836081</v>
       </c>
-      <c r="P28" s="3"/>
+      <c r="P28" s="12">
+        <f>+P26/P29</f>
+        <v>2.8102401432185369</v>
+      </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
@@ -2443,8 +2555,12 @@
       <c r="B29" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="C29" s="3">
+        <v>92.474688</v>
+      </c>
+      <c r="D29" s="3">
+        <v>92.741888000000003</v>
+      </c>
       <c r="E29" s="3">
         <v>92.780736000000005</v>
       </c>
@@ -2476,7 +2592,9 @@
       <c r="O29" s="3">
         <v>87.503853000000007</v>
       </c>
-      <c r="P29" s="3"/>
+      <c r="P29" s="3">
+        <v>85.633606999999998</v>
+      </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -2590,43 +2708,46 @@
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="15" t="e">
+      <c r="G31" s="13" t="e">
         <f t="shared" ref="G31:H31" si="12">+G7/C7-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H31" s="15" t="e">
+      <c r="H31" s="13" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="13">
         <f>+I7/E7-1</f>
         <v>3.5410764872521261E-2</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="13">
         <f t="shared" ref="J31:M31" si="13">+J7/F7-1</f>
         <v>3.82436260623229E-2</v>
       </c>
-      <c r="K31" s="15" t="e">
+      <c r="K31" s="13" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L31" s="15" t="e">
+      <c r="L31" s="13" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M31" s="15">
+      <c r="M31" s="13">
         <f t="shared" si="13"/>
         <v>5.0615595075239384E-2</v>
       </c>
-      <c r="N31" s="15">
+      <c r="N31" s="13">
         <f t="shared" ref="N31" si="14">+N7/J7-1</f>
         <v>6.9577080491132426E-2</v>
       </c>
-      <c r="O31" s="15">
-        <f t="shared" ref="O31" si="15">+O7/K7-1</f>
+      <c r="O31" s="13">
+        <f t="shared" ref="O31:P31" si="15">+O7/K7-1</f>
         <v>8.0491132332878523E-2</v>
       </c>
-      <c r="P31" s="3"/>
+      <c r="P31" s="13">
+        <f t="shared" si="15"/>
+        <v>5.9523809523809534E-2</v>
+      </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
@@ -2676,47 +2797,50 @@
       <c r="B32" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15" t="e">
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13">
         <f t="shared" ref="G32:J36" si="16">+G10/C10-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H32" s="15" t="e">
+        <v>0.11136094924415163</v>
+      </c>
+      <c r="H32" s="13">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I32" s="15">
+        <v>7.359735288735636E-2</v>
+      </c>
+      <c r="I32" s="13">
         <f t="shared" si="16"/>
         <v>6.930280692373314E-2</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="13">
         <f t="shared" si="16"/>
         <v>9.345659608784973E-2</v>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="13">
         <f>+K10/G10-1</f>
         <v>8.272652146242776E-2</v>
       </c>
-      <c r="L32" s="15">
+      <c r="L32" s="13">
         <f>+L10/H10-1</f>
         <v>6.6515550869794327E-2</v>
       </c>
-      <c r="M32" s="15">
+      <c r="M32" s="13">
         <f>+M10/I10-1</f>
         <v>7.9780855656267802E-2</v>
       </c>
-      <c r="N32" s="15">
-        <f t="shared" ref="N32:O36" si="17">+N10/J10-1</f>
+      <c r="N32" s="13">
+        <f t="shared" ref="N32:P36" si="17">+N10/J10-1</f>
         <v>4.2889250770493881E-2</v>
       </c>
-      <c r="O32" s="15">
+      <c r="O32" s="13">
         <f t="shared" si="17"/>
         <v>3.3586521877209563E-2</v>
       </c>
-      <c r="P32" s="3"/>
+      <c r="P32" s="13">
+        <f t="shared" si="17"/>
+        <v>4.5441664442445351E-2</v>
+      </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
@@ -2766,47 +2890,50 @@
       <c r="B33" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15" t="e">
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H33" s="15" t="e">
+        <v>0.16423183005461461</v>
+      </c>
+      <c r="H33" s="13">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I33" s="15">
+        <v>0.10243930422915382</v>
+      </c>
+      <c r="I33" s="13">
         <f t="shared" si="16"/>
         <v>0.10273621643779474</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="13">
         <f t="shared" si="16"/>
         <v>-0.14256927230267269</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="13">
         <f t="shared" ref="K33:M36" si="18">+K11/G11-1</f>
         <v>0.10800744294630249</v>
       </c>
-      <c r="L33" s="15">
+      <c r="L33" s="13">
         <f t="shared" si="18"/>
         <v>0.1366229469584721</v>
       </c>
-      <c r="M33" s="15">
+      <c r="M33" s="13">
         <f t="shared" si="18"/>
         <v>9.1333499154040876E-2</v>
       </c>
-      <c r="N33" s="15">
+      <c r="N33" s="13">
         <f t="shared" si="17"/>
         <v>0.45201823461615231</v>
       </c>
-      <c r="O33" s="15">
+      <c r="O33" s="13">
         <f t="shared" si="17"/>
         <v>0.16597283581413258</v>
       </c>
-      <c r="P33" s="3"/>
+      <c r="P33" s="13">
+        <f t="shared" si="17"/>
+        <v>0.15189608061414783</v>
+      </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
@@ -2856,47 +2983,50 @@
       <c r="B34" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15" t="e">
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H34" s="15" t="e">
+        <v>-0.12455135597393019</v>
+      </c>
+      <c r="H34" s="13">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I34" s="15">
+        <v>-8.5759069810405708E-2</v>
+      </c>
+      <c r="I34" s="13">
         <f t="shared" si="16"/>
         <v>-7.3365703275529826E-2</v>
       </c>
-      <c r="J34" s="15">
+      <c r="J34" s="13">
         <f t="shared" si="16"/>
         <v>-3.3212907243280299E-2</v>
       </c>
-      <c r="K34" s="15">
+      <c r="K34" s="13">
         <f t="shared" si="18"/>
         <v>1.2014445455823752E-2</v>
       </c>
-      <c r="L34" s="15">
+      <c r="L34" s="13">
         <f t="shared" si="18"/>
         <v>5.1958385299085919E-2</v>
       </c>
-      <c r="M34" s="15">
+      <c r="M34" s="13">
         <f t="shared" si="18"/>
         <v>0.13065204589838886</v>
       </c>
-      <c r="N34" s="15">
+      <c r="N34" s="13">
         <f t="shared" si="17"/>
         <v>0.12469183102345416</v>
       </c>
-      <c r="O34" s="15">
+      <c r="O34" s="13">
         <f t="shared" si="17"/>
         <v>0.11415513427542456</v>
       </c>
-      <c r="P34" s="3"/>
+      <c r="P34" s="13">
+        <f t="shared" si="17"/>
+        <v>8.0571238192999939E-2</v>
+      </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
@@ -2946,47 +3076,50 @@
       <c r="B35" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15" t="e">
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H35" s="15" t="e">
+        <v>0.51431902078880887</v>
+      </c>
+      <c r="H35" s="13">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I35" s="15">
+        <v>0.62558026992633486</v>
+      </c>
+      <c r="I35" s="13">
         <f t="shared" si="16"/>
         <v>0.48409548812503811</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="13">
         <f t="shared" si="16"/>
         <v>0.94235890932149657</v>
       </c>
-      <c r="K35" s="15">
+      <c r="K35" s="13">
         <f t="shared" si="18"/>
         <v>0.59546842523928056</v>
       </c>
-      <c r="L35" s="15">
+      <c r="L35" s="13">
         <f t="shared" si="18"/>
         <v>0.53184263914615859</v>
       </c>
-      <c r="M35" s="15">
+      <c r="M35" s="13">
         <f t="shared" si="18"/>
         <v>0.48746297515221326</v>
       </c>
-      <c r="N35" s="15">
+      <c r="N35" s="13">
         <f t="shared" si="17"/>
         <v>0.30997192386797678</v>
       </c>
-      <c r="O35" s="15">
+      <c r="O35" s="13">
         <f t="shared" si="17"/>
         <v>0.34506328706756517</v>
       </c>
-      <c r="P35" s="3"/>
+      <c r="P35" s="13">
+        <f t="shared" si="17"/>
+        <v>0.28555696311864809</v>
+      </c>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
@@ -3036,47 +3169,50 @@
       <c r="B36" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15" t="e">
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H36" s="15" t="e">
+        <v>0.21810161738278055</v>
+      </c>
+      <c r="H36" s="13">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I36" s="15">
+        <v>0.18745684695051801</v>
+      </c>
+      <c r="I36" s="13">
         <f t="shared" si="16"/>
         <v>5.9224102352455565E-2</v>
       </c>
-      <c r="J36" s="15">
+      <c r="J36" s="13">
         <f t="shared" si="16"/>
         <v>0.11395295729618637</v>
       </c>
-      <c r="K36" s="15">
+      <c r="K36" s="13">
         <f t="shared" si="18"/>
         <v>0.15329935622317592</v>
       </c>
-      <c r="L36" s="15">
+      <c r="L36" s="13">
         <f t="shared" si="18"/>
         <v>3.5371644539199387E-2</v>
       </c>
-      <c r="M36" s="15">
+      <c r="M36" s="13">
         <f t="shared" si="18"/>
         <v>4.9386323787258934E-2</v>
       </c>
-      <c r="N36" s="15">
+      <c r="N36" s="13">
         <f t="shared" si="17"/>
         <v>4.9712997129971237E-2</v>
       </c>
-      <c r="O36" s="15">
+      <c r="O36" s="13">
         <f t="shared" si="17"/>
         <v>-4.3028259099896493E-3</v>
       </c>
-      <c r="P36" s="3"/>
+      <c r="P36" s="13">
+        <f t="shared" si="17"/>
+        <v>2.1527517783603844E-3</v>
+      </c>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
@@ -3126,47 +3262,50 @@
       <c r="B37" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="17" t="e">
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="15">
         <f t="shared" ref="G37:M37" si="19">+G18/C18-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H37" s="17" t="e">
+        <v>7.8187959780090299E-2</v>
+      </c>
+      <c r="H37" s="15">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I37" s="17">
+        <v>6.2697935458007725E-2</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="19"/>
         <v>6.2974272034868051E-2</v>
       </c>
-      <c r="J37" s="17">
+      <c r="J37" s="15">
         <f t="shared" si="19"/>
         <v>0.10087915844095718</v>
       </c>
-      <c r="K37" s="17">
+      <c r="K37" s="15">
         <f t="shared" si="19"/>
         <v>0.10724208232977883</v>
       </c>
-      <c r="L37" s="17">
+      <c r="L37" s="15">
         <f t="shared" si="19"/>
         <v>0.11301822022709263</v>
       </c>
-      <c r="M37" s="17">
+      <c r="M37" s="15">
         <f t="shared" si="19"/>
         <v>0.12299033303839235</v>
       </c>
-      <c r="N37" s="17">
+      <c r="N37" s="15">
         <f t="shared" ref="N37" si="20">+N18/J18-1</f>
         <v>0.10124562990489694</v>
       </c>
-      <c r="O37" s="17">
-        <f t="shared" ref="O37" si="21">+O18/K18-1</f>
+      <c r="O37" s="15">
+        <f t="shared" ref="O37:P37" si="21">+O18/K18-1</f>
         <v>0.1142112717478212</v>
       </c>
-      <c r="P37" s="3"/>
+      <c r="P37" s="15">
+        <f t="shared" si="21"/>
+        <v>0.10444225139640673</v>
+      </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
@@ -3216,59 +3355,62 @@
       <c r="B38" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="15" t="e">
+      <c r="C38" s="13">
         <f t="shared" ref="C38:H38" si="22">+C20/C18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D38" s="15" t="e">
+        <v>0.33332908307348386</v>
+      </c>
+      <c r="D38" s="13">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E38" s="15">
+        <v>0.35810626515589195</v>
+      </c>
+      <c r="E38" s="13">
         <f t="shared" si="22"/>
         <v>0.35468016054025442</v>
       </c>
-      <c r="F38" s="15">
+      <c r="F38" s="13">
         <f t="shared" si="22"/>
         <v>0.29214557453468387</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="13">
         <f t="shared" si="22"/>
         <v>0.34011336418118282</v>
       </c>
-      <c r="H38" s="15">
+      <c r="H38" s="13">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
-      <c r="I38" s="15">
+      <c r="I38" s="13">
         <f>+I20/I18</f>
         <v>0.36517764372859085</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="13">
         <f>+J20/J18</f>
         <v>0.32251974182822768</v>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="13">
         <f>+K20/K18</f>
         <v>0.36785530811936207</v>
       </c>
-      <c r="L38" s="15">
+      <c r="L38" s="13">
         <f>+L20/L18</f>
         <v>0.37624796063146493</v>
       </c>
-      <c r="M38" s="15">
+      <c r="M38" s="13">
         <f>+M20/M18</f>
         <v>0.36834406774119721</v>
       </c>
-      <c r="N38" s="15">
+      <c r="N38" s="13">
         <f t="shared" ref="N38:O38" si="23">+N20/N18</f>
         <v>0.33256242472679642</v>
       </c>
-      <c r="O38" s="15">
+      <c r="O38" s="13">
         <f t="shared" si="23"/>
         <v>0.36626579223610978</v>
       </c>
-      <c r="P38" s="3"/>
+      <c r="P38" s="13">
+        <f t="shared" ref="P38" si="24">+P20/P18</f>
+        <v>0.43416841414873802</v>
+      </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
@@ -3318,59 +3460,62 @@
       <c r="B39" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="15" t="e">
-        <f t="shared" ref="C39:H39" si="24">+C22/C18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D39" s="15" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E39" s="15">
-        <f t="shared" si="24"/>
+      <c r="C39" s="13">
+        <f t="shared" ref="C39:H39" si="25">+C22/C18</f>
+        <v>6.4082903772740216E-2</v>
+      </c>
+      <c r="D39" s="13">
+        <f t="shared" si="25"/>
+        <v>0.10383471087372605</v>
+      </c>
+      <c r="E39" s="13">
+        <f t="shared" si="25"/>
         <v>8.5061045572264155E-2</v>
       </c>
-      <c r="F39" s="15">
-        <f t="shared" si="24"/>
+      <c r="F39" s="13">
+        <f t="shared" si="25"/>
         <v>3.8579081869527097E-2</v>
       </c>
-      <c r="G39" s="15">
-        <f t="shared" si="24"/>
+      <c r="G39" s="13">
+        <f t="shared" si="25"/>
         <v>6.2148755925552052E-2</v>
       </c>
-      <c r="H39" s="15">
-        <f t="shared" si="24"/>
+      <c r="H39" s="13">
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="13">
         <f>+I22/I18</f>
         <v>9.4496844377705475E-2</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="13">
         <f>+J22/J18</f>
         <v>7.6592181502579154E-2</v>
       </c>
-      <c r="K39" s="15">
+      <c r="K39" s="13">
         <f>+K22/K18</f>
         <v>9.6439942504744247E-2</v>
       </c>
-      <c r="L39" s="15">
+      <c r="L39" s="13">
         <f>+L22/L18</f>
         <v>0.1158906267133188</v>
       </c>
-      <c r="M39" s="15">
+      <c r="M39" s="13">
         <f>+M22/M18</f>
         <v>9.4366234020989245E-2</v>
       </c>
-      <c r="N39" s="15">
-        <f t="shared" ref="N39:O39" si="25">+N22/N18</f>
+      <c r="N39" s="13">
+        <f t="shared" ref="N39:O39" si="26">+N22/N18</f>
         <v>8.8080609622759848E-2</v>
       </c>
-      <c r="O39" s="15">
-        <f t="shared" si="25"/>
+      <c r="O39" s="13">
+        <f t="shared" si="26"/>
         <v>9.4293361775953641E-2</v>
       </c>
-      <c r="P39" s="3"/>
+      <c r="P39" s="13">
+        <f t="shared" ref="P39" si="27">+P22/P18</f>
+        <v>0.1737387291167117</v>
+      </c>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
@@ -3420,59 +3565,62 @@
       <c r="B40" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="15" t="e">
-        <f t="shared" ref="C40:H40" si="26">+C25/C24</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D40" s="15" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E40" s="15">
-        <f t="shared" si="26"/>
+      <c r="C40" s="13">
+        <f t="shared" ref="C40:H40" si="28">+C25/C24</f>
+        <v>0.27056561129730561</v>
+      </c>
+      <c r="D40" s="13">
+        <f t="shared" si="28"/>
+        <v>0.23177634929186641</v>
+      </c>
+      <c r="E40" s="13">
+        <f t="shared" si="28"/>
         <v>0.24314615756315941</v>
       </c>
-      <c r="F40" s="15">
-        <f t="shared" si="26"/>
+      <c r="F40" s="13">
+        <f t="shared" si="28"/>
         <v>0.25418196017180811</v>
       </c>
-      <c r="G40" s="15">
-        <f t="shared" si="26"/>
+      <c r="G40" s="13">
+        <f t="shared" si="28"/>
         <v>0.23624335353035747</v>
       </c>
-      <c r="H40" s="15">
-        <f t="shared" si="26"/>
+      <c r="H40" s="13">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="13">
         <f>+I25/I24</f>
         <v>0.24236556923258129</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="13">
         <f>+J25/J24</f>
         <v>8.1012329457778989E-2</v>
       </c>
-      <c r="K40" s="15">
+      <c r="K40" s="13">
         <f>+K25/K24</f>
         <v>0.21416913892777611</v>
       </c>
-      <c r="L40" s="15">
+      <c r="L40" s="13">
         <f>+L25/L24</f>
         <v>0.2150234895483786</v>
       </c>
-      <c r="M40" s="15">
+      <c r="M40" s="13">
         <f>+M25/M24</f>
         <v>0.23617698186231112</v>
       </c>
-      <c r="N40" s="15">
-        <f t="shared" ref="N40:O40" si="27">+N25/N24</f>
+      <c r="N40" s="13">
+        <f t="shared" ref="N40:O40" si="29">+N25/N24</f>
         <v>0.21928373315167143</v>
       </c>
-      <c r="O40" s="15">
-        <f t="shared" si="27"/>
+      <c r="O40" s="13">
+        <f t="shared" si="29"/>
         <v>0.20677196879327597</v>
       </c>
-      <c r="P40" s="3"/>
+      <c r="P40" s="13">
+        <f t="shared" ref="P40" si="30">+P25/P24</f>
+        <v>0.1939070141354593</v>
+      </c>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
